--- a/study-guides/React-Workshop-3-Day-Curriculum.xlsx
+++ b/study-guides/React-Workshop-3-Day-Curriculum.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>88 labs, each marked core / depth / optional. A 3-day delivery demos the CORE labs; depth labs are self-study.</t>
+          <t>91 labs, each marked core / depth / optional. A 3-day delivery demos the CORE labs; depth labs are self-study.</t>
         </is>
       </c>
     </row>
@@ -927,29 +927,41 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>105 minutes and four build steps. If the room is behind, cut Lab 17.5 (TanStack Query) and Lab 18.1, and set build steps 13 and 15 as self-study.</t>
+          <t>105 minutes, three sections and four build steps. §18 alone has 12 subsections and 5 labs. Demo only the core labs listed for S13; 17.3/17.4/17.5/17.7 and 18.2/18.4/18.5 are written to be worked alone.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>§22 and §23 are alternatives</t>
+          <t>Routing has more depth than one session holds</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Both are fully written with labs. If session 15 is tight, demo Zustand (2 labs, faster payoff) and leave Redux as reading — or the reverse if the audience's employer already uses Redux.</t>
+          <t>§18 covers the server-side SPA fallback, nested/pathless routes, Outlet context, routes-as-config and the data router. If the audience deploys their own apps, the §18.2 server-config material is the highest-value 10 minutes of Day 3 — it is the most common production bug in React apps.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>§22 and §23 are alternatives</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Both are fully written with labs. If session 15 is tight, demo Zustand (2 labs, faster payoff) and leave Redux as reading — or the reverse if the audience's employer already uses Redux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>If a day runs long</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>The compressible parts are: Lab 2.3, Lab 6.5, Labs 11.3/11.5, Lab 15.3, Lab 16.4, Lab 20.2. All are marked depth or optional.</t>
         </is>
@@ -1885,7 +1897,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="95" customHeight="1">
+    <row r="23" ht="121" customHeight="1">
       <c r="A23" s="27" t="inlineStr">
         <is>
           <t>S13</t>
@@ -1917,22 +1929,28 @@
 axios.isAxiosError / isCancel; a custom AxiosAdapter for offline mocks
 In production use a library — TanStack Query shown for comparison
 Routing: Routes/Route/Outlet/NavLink, useParams, THE URL IS STATE (useSearchParams)
-Code splitting routes; protected routes; a note on data routers
+Choosing a router, and the SPA fallback BrowserRouter needs on the server (the #1 works-locally-404s-in-production bug)
+Nested + layout + index + pathless routes; Outlet context; relative links; params are always string|undefined
+Routes as DATA (RouteObject[] + useRoutes), so the nav can be generated from the config
+Code splitting routes; protected routes as a layout route; data routers with loaders and errorElement
 Error boundaries (class components, getDerivedStateFromError) and what they DON'T catch; Suspense + lazy</t>
         </is>
       </c>
       <c r="G23" s="30" t="inlineStr">
         <is>
-          <t>17.1 Fetching by hand
+          <t>DEMO (core): 17.1 Fetching by hand
 17.2 The race condition
-17.3 useFetch with union state
+17.6 axios vs fetch
+18.1 A real router
+18.3 A nested-route app
+19.1 Error boundaries
+SELF-STUDY: 17.3 useFetch
 17.4 Validate at the boundary
 17.5 TanStack Query
-17.6 axios vs fetch
-17.7 An instance with interceptors
-18.1 A real router
-18.2 The URL as state
-19.1 Error boundaries
+17.7 Interceptors
+18.2 URL as state
+18.4 Routes as a config
+18.5 Data router &amp; loaders
 19.2 Suspense &amp; lazy</t>
         </is>
       </c>
@@ -1943,7 +1961,7 @@
       </c>
       <c r="I23" s="30" t="inlineStr">
         <is>
-          <t>Do Build Steps 12, 13, 14, 15. Concept checks §17, §18, §19.</t>
+          <t>Do Build Steps 12, 13, 14, 15. Work Labs 18.4 and 18.5 (route config, then the data router) — both reuse Lab 18.3's files. Concept checks §17, §18 (13 questions), §19.</t>
         </is>
       </c>
       <c r="J23" s="30" t="inlineStr">
@@ -3137,7 +3155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3149,7 +3167,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>ALL 88 LABS — React-Demo-Guide.md</t>
+          <t>ALL 91 LABS — React-Demo-Guide.md</t>
         </is>
       </c>
     </row>
@@ -4757,199 +4775,199 @@
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="43" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>Error boundaries</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>19 Errors &amp; Suspense</t>
-        </is>
-      </c>
-      <c r="D82" s="43" t="n">
+      <c r="A82" s="37" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="B82" s="39" t="inlineStr">
+        <is>
+          <t>A complete nested-route app, in its own files</t>
+        </is>
+      </c>
+      <c r="C82" s="39" t="inlineStr">
+        <is>
+          <t>18 Routing</t>
+        </is>
+      </c>
+      <c r="D82" s="37" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="43" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>Suspense and lazy</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>19 Errors &amp; Suspense</t>
-        </is>
-      </c>
-      <c r="D83" s="43" t="n">
+      <c r="A83" s="37" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="B83" s="39" t="inlineStr">
+        <is>
+          <t>The same app, driven by a route config</t>
+        </is>
+      </c>
+      <c r="C83" s="39" t="inlineStr">
+        <is>
+          <t>18 Routing</t>
+        </is>
+      </c>
+      <c r="D83" s="37" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="37" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="B84" s="39" t="inlineStr">
         <is>
-          <t>Compound components</t>
+          <t>The data router: loaders instead of effects</t>
         </is>
       </c>
       <c r="C84" s="39" t="inlineStr">
         <is>
-          <t>20 Patterns</t>
+          <t>18 Routing</t>
         </is>
       </c>
       <c r="D84" s="37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="37" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
-      </c>
-      <c r="B85" s="39" t="inlineStr">
-        <is>
-          <t>Render props vs a custom hook</t>
-        </is>
-      </c>
-      <c r="C85" s="39" t="inlineStr">
-        <is>
-          <t>20 Patterns</t>
-        </is>
-      </c>
-      <c r="D85" s="37" t="n">
-        <v>14</v>
+      <c r="A85" s="43" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Error boundaries</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>19 Errors &amp; Suspense</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="43" t="inlineStr">
         <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Suspense and lazy</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>19 Errors &amp; Suspense</t>
+        </is>
+      </c>
+      <c r="D86" s="43" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="37" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="B87" s="39" t="inlineStr">
+        <is>
+          <t>Compound components</t>
+        </is>
+      </c>
+      <c r="C87" s="39" t="inlineStr">
+        <is>
+          <t>20 Patterns</t>
+        </is>
+      </c>
+      <c r="D87" s="37" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="37" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="B88" s="39" t="inlineStr">
+        <is>
+          <t>Render props vs a custom hook</t>
+        </is>
+      </c>
+      <c r="C88" s="39" t="inlineStr">
+        <is>
+          <t>20 Patterns</t>
+        </is>
+      </c>
+      <c r="D88" s="37" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="43" t="inlineStr">
+        <is>
           <t>21.1</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>Testing a component's behaviour</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>21 Testing</t>
         </is>
       </c>
-      <c r="D86" s="43" t="n">
+      <c r="D89" s="43" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="43" t="inlineStr">
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="43" t="inlineStr">
         <is>
           <t>21.2</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>Testing hooks and async behaviour</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>21 Testing</t>
         </is>
       </c>
-      <c r="D87" s="43" t="n">
+      <c r="D90" s="43" t="n">
         <v>14</v>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="45" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="B88" s="47" t="inlineStr">
-        <is>
-          <t>A store, a slice, and typed hooks</t>
-        </is>
-      </c>
-      <c r="C88" s="47" t="inlineStr">
-        <is>
-          <t>22 Redux Toolkit</t>
-        </is>
-      </c>
-      <c r="D88" s="45" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="45" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="B89" s="47" t="inlineStr">
-        <is>
-          <t>A tasks slice, and the selector traps</t>
-        </is>
-      </c>
-      <c r="C89" s="47" t="inlineStr">
-        <is>
-          <t>22 Redux Toolkit</t>
-        </is>
-      </c>
-      <c r="D89" s="45" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="45" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="B90" s="47" t="inlineStr">
-        <is>
-          <t>createAsyncThunk with axios and zod</t>
-        </is>
-      </c>
-      <c r="C90" s="47" t="inlineStr">
-        <is>
-          <t>22 Redux Toolkit</t>
-        </is>
-      </c>
-      <c r="D90" s="45" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="45" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="B91" s="47" t="inlineStr">
         <is>
-          <t>A store in ten lines, and the selector trap</t>
+          <t>A store, a slice, and typed hooks</t>
         </is>
       </c>
       <c r="C91" s="47" t="inlineStr">
         <is>
-          <t>23 Zustand</t>
+          <t>22 Redux Toolkit</t>
         </is>
       </c>
       <c r="D91" s="45" t="n">
@@ -4959,20 +4977,80 @@
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="45" t="inlineStr">
         <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="B92" s="47" t="inlineStr">
+        <is>
+          <t>A tasks slice, and the selector traps</t>
+        </is>
+      </c>
+      <c r="C92" s="47" t="inlineStr">
+        <is>
+          <t>22 Redux Toolkit</t>
+        </is>
+      </c>
+      <c r="D92" s="45" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="45" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="B93" s="47" t="inlineStr">
+        <is>
+          <t>createAsyncThunk with axios and zod</t>
+        </is>
+      </c>
+      <c r="C93" s="47" t="inlineStr">
+        <is>
+          <t>22 Redux Toolkit</t>
+        </is>
+      </c>
+      <c r="D93" s="45" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="45" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="B94" s="47" t="inlineStr">
+        <is>
+          <t>A store in ten lines, and the selector trap</t>
+        </is>
+      </c>
+      <c r="C94" s="47" t="inlineStr">
+        <is>
+          <t>23 Zustand</t>
+        </is>
+      </c>
+      <c r="D94" s="45" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="45" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="B92" s="47" t="inlineStr">
+      <c r="B95" s="47" t="inlineStr">
         <is>
           <t>persist, devtools, immer — and validating on rehydrate</t>
         </is>
       </c>
-      <c r="C92" s="47" t="inlineStr">
+      <c r="C95" s="47" t="inlineStr">
         <is>
           <t>23 Zustand</t>
         </is>
       </c>
-      <c r="D92" s="45" t="n">
+      <c r="D95" s="45" t="n">
         <v>15</v>
       </c>
     </row>
